--- a/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
+++ b/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Models\US\Models\eps-us\InputData\elec\SoFCtMbCtPR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\elec\SoFCtMbCtPR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79CF789-70E7-4DC0-88EA-1AD99B90A68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9541C3-C216-43DA-9833-DBF43E70A8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7650" yWindow="9600" windowWidth="23010" windowHeight="13770" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="19240" windowHeight="11270" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -160,11 +160,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -172,7 +172,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -180,8 +180,15 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -211,7 +218,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -227,7 +234,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -523,15 +530,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DA106A-E484-4E2B-B3F9-91B326CF3E2A}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,7 +547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -547,63 +555,64 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ABB53E3-B52E-4F21-A58E-08755890D033}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+    <col min="1" max="1" width="34.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -611,7 +620,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -619,7 +628,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -627,7 +636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -635,7 +644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -643,7 +652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -651,7 +660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -659,7 +668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -667,7 +676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -675,7 +684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -683,7 +692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -691,7 +700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -699,7 +708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -707,7 +716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -715,7 +724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -723,7 +732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -731,7 +740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -739,7 +748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -747,7 +756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -755,7 +764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -763,7 +772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -771,7 +780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -779,7 +788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -787,7 +796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -795,7 +804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -804,6 +813,178 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C583494C-EB6A-4C62-A5C9-B4C4FB517B28}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D672DA8-8491-4F46-B34A-09F7EB1F7A22}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F87749F-8CD6-4CCE-826B-4D11FAAE7217}"/>
 </file>
--- a/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
+++ b/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
@@ -978,13 +978,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C583494C-EB6A-4C62-A5C9-B4C4FB517B28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00313796-8232-4A46-A1A7-BA54812B352B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D672DA8-8491-4F46-B34A-09F7EB1F7A22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75903D36-E21A-476E-BEDE-292264C9887F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F87749F-8CD6-4CCE-826B-4D11FAAE7217}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E449932-7465-49FF-87F3-D3C46ACC27B0}"/>
 </file>
--- a/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
+++ b/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\elec\SoFCtMbCtPR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\elec\SoFCtMbCtPR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9541C3-C216-43DA-9833-DBF43E70A8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2636D6B6-13BD-45A3-A0ED-794BAA95170F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="19240" windowHeight="11270" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
+    <workbookView xWindow="2700" yWindow="3060" windowWidth="43200" windowHeight="17145" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Source:</t>
   </si>
@@ -127,44 +127,17 @@
   </si>
   <si>
     <t>Notes:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In the US, many coal plants are subject to rules requiring them </t>
-  </si>
-  <si>
-    <t>to retrofit to meet enviromental guidelines. This requires</t>
-  </si>
-  <si>
-    <t>a one time investment decision for plant owners. Because we don't</t>
-  </si>
-  <si>
-    <t>track individual plants in the model, we calibrate the share of forward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">costs that must be recovered to represent the additional revenue that is needed to </t>
-  </si>
-  <si>
-    <t>save and pay for these one time investments and apply this across the distribution</t>
-  </si>
-  <si>
-    <t>of plant types. Calibration is done by comparing model results against other sources,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">including Rhodium's ClimateDeck and EIA's Annual Energy Outlook and Electric </t>
-  </si>
-  <si>
-    <t>Power Monthly.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -172,7 +145,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -180,13 +153,13 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -218,7 +191,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -234,7 +207,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -531,15 +504,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DA106A-E484-4E2B-B3F9-91B326CF3E2A}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,52 +520,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -607,12 +537,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.58203125" customWidth="1"/>
+    <col min="1" max="1" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -620,15 +550,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -636,7 +566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -644,7 +574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -652,7 +582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -660,7 +590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -668,7 +598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -676,7 +606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -684,7 +614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -692,7 +622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -700,7 +630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -708,7 +638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -716,7 +646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -724,7 +654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -732,7 +662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -740,7 +670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -748,7 +678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -756,7 +686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -764,7 +694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -772,7 +702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -780,7 +710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -788,7 +718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -796,7 +726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -804,7 +734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -819,6 +749,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -962,15 +901,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -978,13 +908,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00313796-8232-4A46-A1A7-BA54812B352B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75903D36-E21A-476E-BEDE-292264C9887F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75903D36-E21A-476E-BEDE-292264C9887F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00313796-8232-4A46-A1A7-BA54812B352B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E449932-7465-49FF-87F3-D3C46ACC27B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E449932-7465-49FF-87F3-D3C46ACC27B0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>